--- a/data/raw/Kawak/2026.xlsx
+++ b/data/raw/Kawak/2026.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/Kawak/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F92E75E-B59D-4BE1-AA06-AE9DF1255F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{2F92E75E-B59D-4BE1-AA06-AE9DF1255F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B093890-10EB-4268-A34D-32C4F54B2AC7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EC61DB77-57A8-42E6-851D-6E7603E23E56}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$O$786</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
@@ -3525,6 +3530,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -3998,14 +4004,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15ED7BC6-9428-429B-AFE1-AE8C1E13D30C}">
-  <dimension ref="A1:AA786"/>
+  <dimension ref="A1:Z786"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="27" width="9.109375" customWidth="1"/>
-    <col min="28" max="256" width="8.88671875" customWidth="1"/>
+    <col min="1" max="26" width="9.109375" customWidth="1"/>
+    <col min="27" max="255" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4062,9 +4068,8 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>68</v>
       </c>
@@ -4109,7 +4114,7 @@
         <v>85.3</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>69</v>
       </c>
@@ -4156,7 +4161,7 @@
         <v>90.14</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>73</v>
       </c>
@@ -4203,7 +4208,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>74</v>
       </c>
@@ -4250,7 +4255,7 @@
         <v>91.49</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>77</v>
       </c>
@@ -4295,7 +4300,7 @@
         <v>94.9</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>84</v>
       </c>
@@ -4342,7 +4347,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>85</v>
       </c>
@@ -4389,7 +4394,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>86</v>
       </c>
@@ -4436,7 +4441,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>87</v>
       </c>
@@ -4483,7 +4488,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>88</v>
       </c>
@@ -4530,7 +4535,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>89</v>
       </c>
@@ -4577,7 +4582,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>90</v>
       </c>
@@ -4624,7 +4629,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>91</v>
       </c>
@@ -4671,7 +4676,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>92</v>
       </c>
@@ -4718,7 +4723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>94</v>
       </c>

--- a/data/raw/Kawak/2026.xlsx
+++ b/data/raw/Kawak/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{2F92E75E-B59D-4BE1-AA06-AE9DF1255F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E61E940A-7B43-496C-82A3-6A250CBF2E10}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{2F92E75E-B59D-4BE1-AA06-AE9DF1255F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D0D2F8F-17AC-4DD4-ABFA-00D6A65E4454}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EC61DB77-57A8-42E6-851D-6E7603E23E56}"/>
   </bookViews>
@@ -3685,6 +3685,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/raw/Kawak/2026.xlsx
+++ b/data/raw/Kawak/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{2F92E75E-B59D-4BE1-AA06-AE9DF1255F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D0D2F8F-17AC-4DD4-ABFA-00D6A65E4454}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{2F92E75E-B59D-4BE1-AA06-AE9DF1255F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{306875E5-84A1-4559-A51F-2E6495B28CFE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EC61DB77-57A8-42E6-851D-6E7603E23E56}"/>
   </bookViews>
@@ -3685,10 +3685,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4008,6 +4004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15ED7BC6-9428-429B-AFE1-AE8C1E13D30C}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y786"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4072,7 +4069,7 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>68</v>
       </c>
@@ -4117,7 +4114,7 @@
         <v>85.3</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>69</v>
       </c>
@@ -4164,7 +4161,7 @@
         <v>90.14</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>73</v>
       </c>
@@ -4211,7 +4208,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>74</v>
       </c>
@@ -4258,7 +4255,7 @@
         <v>91.49</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>77</v>
       </c>
@@ -4303,7 +4300,7 @@
         <v>94.9</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>84</v>
       </c>
@@ -4350,7 +4347,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>85</v>
       </c>
@@ -4397,7 +4394,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>86</v>
       </c>
@@ -4444,7 +4441,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>87</v>
       </c>
@@ -4491,7 +4488,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>88</v>
       </c>
@@ -4538,7 +4535,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>89</v>
       </c>
@@ -4585,7 +4582,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>90</v>
       </c>
@@ -4632,7 +4629,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>91</v>
       </c>
@@ -4679,7 +4676,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>92</v>
       </c>
@@ -4726,7 +4723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>94</v>
       </c>
@@ -4773,7 +4770,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>95</v>
       </c>
@@ -4820,7 +4817,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>100</v>
       </c>
@@ -4867,7 +4864,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>104</v>
       </c>
@@ -4914,7 +4911,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>106</v>
       </c>
@@ -5008,7 +5005,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>111</v>
       </c>
@@ -5055,7 +5052,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>112</v>
       </c>
@@ -5102,7 +5099,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>113</v>
       </c>
@@ -5149,7 +5146,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>114</v>
       </c>
@@ -5196,7 +5193,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>115</v>
       </c>
@@ -5243,7 +5240,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>116</v>
       </c>
@@ -5290,7 +5287,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>117</v>
       </c>
@@ -5337,7 +5334,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>118</v>
       </c>
@@ -5384,7 +5381,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>121</v>
       </c>
@@ -5431,7 +5428,7 @@
         <v>98.65</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>122</v>
       </c>
@@ -5478,7 +5475,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>124</v>
       </c>
@@ -5525,7 +5522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>125</v>
       </c>
@@ -5572,7 +5569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>126</v>
       </c>
@@ -5619,7 +5616,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>127</v>
       </c>
@@ -5666,7 +5663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>128</v>
       </c>
@@ -5713,7 +5710,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>133</v>
       </c>
@@ -5760,7 +5757,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>143</v>
       </c>
@@ -5807,7 +5804,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>144</v>
       </c>
@@ -5854,7 +5851,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>145</v>
       </c>
@@ -5901,7 +5898,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>146</v>
       </c>
@@ -5948,7 +5945,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>147</v>
       </c>
@@ -5995,7 +5992,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>148</v>
       </c>
@@ -6042,7 +6039,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>150</v>
       </c>
@@ -6087,7 +6084,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>151</v>
       </c>
@@ -6134,7 +6131,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>159</v>
       </c>
@@ -6178,7 +6175,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>167</v>
       </c>
@@ -6225,7 +6222,7 @@
         <v>93.63</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>172</v>
       </c>
@@ -6272,7 +6269,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>193</v>
       </c>
@@ -6319,7 +6316,7 @@
         <v>96.21</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>197</v>
       </c>
@@ -6366,7 +6363,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>199</v>
       </c>
@@ -6413,7 +6410,7 @@
         <v>92.1</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>200</v>
       </c>
@@ -6460,7 +6457,7 @@
         <v>87.4</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>202</v>
       </c>
@@ -6507,7 +6504,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>203</v>
       </c>
@@ -6554,7 +6551,7 @@
         <v>111.77</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>203</v>
       </c>
@@ -6601,7 +6598,7 @@
         <v>110.78</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>203</v>
       </c>
@@ -6648,7 +6645,7 @@
         <v>128.41</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>203</v>
       </c>
@@ -6695,7 +6692,7 @@
         <v>115.28</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>204</v>
       </c>
@@ -6742,7 +6739,7 @@
         <v>86.89</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>205</v>
       </c>
@@ -6789,7 +6786,7 @@
         <v>186.31</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>206</v>
       </c>
@@ -6836,7 +6833,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>207</v>
       </c>
@@ -6883,7 +6880,7 @@
         <v>110.9</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>208</v>
       </c>
@@ -6926,7 +6923,7 @@
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>208</v>
       </c>
@@ -6973,7 +6970,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>208</v>
       </c>
@@ -7020,7 +7017,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>208</v>
       </c>
@@ -7067,7 +7064,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>208</v>
       </c>
@@ -7114,7 +7111,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>208</v>
       </c>
@@ -7161,7 +7158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>208</v>
       </c>
@@ -7208,7 +7205,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>213</v>
       </c>
@@ -7255,7 +7252,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>213</v>
       </c>
@@ -7302,7 +7299,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>213</v>
       </c>
@@ -7349,7 +7346,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>213</v>
       </c>
@@ -7396,7 +7393,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>213</v>
       </c>
@@ -7443,7 +7440,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>213</v>
       </c>
@@ -7490,7 +7487,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>213</v>
       </c>
@@ -7537,7 +7534,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>213</v>
       </c>
@@ -7584,7 +7581,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>213</v>
       </c>
@@ -7631,7 +7628,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>214</v>
       </c>
@@ -7674,7 +7671,7 @@
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>214</v>
       </c>
@@ -7721,7 +7718,7 @@
         <v>789.85</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>214</v>
       </c>
@@ -7768,7 +7765,7 @@
         <v>349.4</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>214</v>
       </c>
@@ -7815,7 +7812,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>214</v>
       </c>
@@ -7862,7 +7859,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>214</v>
       </c>
@@ -7909,7 +7906,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>214</v>
       </c>
@@ -7956,7 +7953,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>215</v>
       </c>
@@ -8003,7 +8000,7 @@
         <v>-114.55</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>215</v>
       </c>
@@ -8050,7 +8047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>215</v>
       </c>
@@ -8097,7 +8094,7 @@
         <v>22.22</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>215</v>
       </c>
@@ -8144,7 +8141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>215</v>
       </c>
@@ -8191,7 +8188,7 @@
         <v>-16.670000000000002</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>215</v>
       </c>
@@ -8238,7 +8235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>215</v>
       </c>
@@ -8285,7 +8282,7 @@
         <v>-255.06</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>216</v>
       </c>
@@ -8332,7 +8329,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>216</v>
       </c>
@@ -8379,7 +8376,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>216</v>
       </c>
@@ -8426,7 +8423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>216</v>
       </c>
@@ -8473,7 +8470,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>216</v>
       </c>
@@ -8520,7 +8517,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>216</v>
       </c>
@@ -8567,7 +8564,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>216</v>
       </c>
@@ -8614,7 +8611,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>217</v>
       </c>
@@ -8657,7 +8654,7 @@
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>217</v>
       </c>
@@ -8704,7 +8701,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>217</v>
       </c>
@@ -8751,7 +8748,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>217</v>
       </c>
@@ -8798,7 +8795,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>217</v>
       </c>
@@ -8845,7 +8842,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>217</v>
       </c>
@@ -8892,7 +8889,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>217</v>
       </c>
@@ -8939,7 +8936,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>218</v>
       </c>
@@ -8982,7 +8979,7 @@
       <c r="N106" s="3"/>
       <c r="O106" s="3"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>218</v>
       </c>
@@ -9029,7 +9026,7 @@
         <v>50967.4</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>218</v>
       </c>
@@ -9076,7 +9073,7 @@
         <v>29640</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>218</v>
       </c>
@@ -9123,7 +9120,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>218</v>
       </c>
@@ -9170,7 +9167,7 @@
         <v>3827</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>218</v>
       </c>
@@ -9217,7 +9214,7 @@
         <v>4495</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>218</v>
       </c>
@@ -9264,7 +9261,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>219</v>
       </c>
@@ -9311,7 +9308,7 @@
         <v>18.43</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>219</v>
       </c>
@@ -9358,7 +9355,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>219</v>
       </c>
@@ -9405,7 +9402,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>219</v>
       </c>
@@ -9452,7 +9449,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>219</v>
       </c>
@@ -9499,7 +9496,7 @@
         <v>38.19</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>219</v>
       </c>
@@ -9546,7 +9543,7 @@
         <v>96.45</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>219</v>
       </c>
@@ -9593,7 +9590,7 @@
         <v>-54.95</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>219</v>
       </c>
@@ -9633,7 +9630,7 @@
       <c r="N120" s="3"/>
       <c r="O120" s="3"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>220</v>
       </c>
@@ -9680,7 +9677,7 @@
         <v>33.979999999999997</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>220</v>
       </c>
@@ -9727,7 +9724,7 @@
         <v>26.83</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>220</v>
       </c>
@@ -9774,7 +9771,7 @@
         <v>-0.72</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>220</v>
       </c>
@@ -9821,7 +9818,7 @@
         <v>-37.380000000000003</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>220</v>
       </c>
@@ -9868,7 +9865,7 @@
         <v>64.709999999999994</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>220</v>
       </c>
@@ -9913,7 +9910,7 @@
       </c>
       <c r="O126" s="3"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>220</v>
       </c>
@@ -9960,7 +9957,7 @@
         <v>98.76</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>221</v>
       </c>
@@ -10007,7 +10004,7 @@
         <v>33.33</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>221</v>
       </c>
@@ -10054,7 +10051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>221</v>
       </c>
@@ -10101,7 +10098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>221</v>
       </c>
@@ -10148,7 +10145,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>221</v>
       </c>
@@ -10195,7 +10192,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>221</v>
       </c>
@@ -10242,7 +10239,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>221</v>
       </c>
@@ -10289,7 +10286,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>222</v>
       </c>
@@ -10336,7 +10333,7 @@
         <v>68.75</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>222</v>
       </c>
@@ -10383,7 +10380,7 @@
         <v>68.75</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>223</v>
       </c>
@@ -10430,7 +10427,7 @@
         <v>94.12</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>223</v>
       </c>
@@ -10477,7 +10474,7 @@
         <v>92.86</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>223</v>
       </c>
@@ -10524,7 +10521,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>224</v>
       </c>
@@ -10571,7 +10568,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>224</v>
       </c>
@@ -10618,7 +10615,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>224</v>
       </c>
@@ -10665,7 +10662,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>224</v>
       </c>
@@ -10712,7 +10709,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>224</v>
       </c>
@@ -10759,7 +10756,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>224</v>
       </c>
@@ -10806,7 +10803,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>224</v>
       </c>
@@ -10853,7 +10850,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>225</v>
       </c>
@@ -10896,7 +10893,7 @@
       <c r="N147" s="3"/>
       <c r="O147" s="3"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>225</v>
       </c>
@@ -10943,7 +10940,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>225</v>
       </c>
@@ -10990,7 +10987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>225</v>
       </c>
@@ -11037,7 +11034,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>225</v>
       </c>
@@ -11084,7 +11081,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>225</v>
       </c>
@@ -11131,7 +11128,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>225</v>
       </c>
@@ -11178,7 +11175,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>226</v>
       </c>
@@ -11223,7 +11220,7 @@
         <v>737.66</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>226</v>
       </c>
@@ -11270,7 +11267,7 @@
         <v>508.91</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>226</v>
       </c>
@@ -11317,7 +11314,7 @@
         <v>126.74</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>226</v>
       </c>
@@ -11364,7 +11361,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>226</v>
       </c>
@@ -11411,7 +11408,7 @@
         <v>76.86</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>226</v>
       </c>
@@ -11458,7 +11455,7 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>226</v>
       </c>
@@ -11505,7 +11502,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>227</v>
       </c>
@@ -11550,7 +11547,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>227</v>
       </c>
@@ -11597,7 +11594,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>227</v>
       </c>
@@ -11644,7 +11641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>227</v>
       </c>
@@ -11691,7 +11688,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>227</v>
       </c>
@@ -11738,7 +11735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>227</v>
       </c>
@@ -11785,7 +11782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>227</v>
       </c>
@@ -11832,7 +11829,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>228</v>
       </c>
@@ -11877,7 +11874,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>228</v>
       </c>
@@ -11924,7 +11921,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>228</v>
       </c>
@@ -11971,7 +11968,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>228</v>
       </c>
@@ -12018,7 +12015,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>228</v>
       </c>
@@ -12065,7 +12062,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>228</v>
       </c>
@@ -12112,7 +12109,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>228</v>
       </c>
@@ -12159,7 +12156,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>230</v>
       </c>
@@ -12206,7 +12203,7 @@
         <v>96.77</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>231</v>
       </c>
@@ -12253,7 +12250,7 @@
         <v>570.89</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>232</v>
       </c>
@@ -12300,7 +12297,7 @@
         <v>85.71</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>233</v>
       </c>
@@ -12347,7 +12344,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>234</v>
       </c>
@@ -12394,7 +12391,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>235</v>
       </c>
@@ -12439,7 +12436,7 @@
         <v>92.012779552715998</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>236</v>
       </c>
@@ -12486,7 +12483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>238</v>
       </c>
@@ -12533,7 +12530,7 @@
         <v>94.59</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>238</v>
       </c>
@@ -12580,7 +12577,7 @@
         <v>94.74</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>238</v>
       </c>
@@ -12627,7 +12624,7 @@
         <v>88.89</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>238</v>
       </c>
@@ -12674,7 +12671,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>238</v>
       </c>
@@ -12721,7 +12718,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>238</v>
       </c>
@@ -12768,7 +12765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>238</v>
       </c>
@@ -12815,7 +12812,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>238</v>
       </c>
@@ -12862,7 +12859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>238</v>
       </c>
@@ -12909,7 +12906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>239</v>
       </c>
@@ -12956,7 +12953,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>239</v>
       </c>
@@ -13003,7 +13000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>239</v>
       </c>
@@ -13050,7 +13047,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>239</v>
       </c>
@@ -13097,7 +13094,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>239</v>
       </c>
@@ -13144,7 +13141,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>239</v>
       </c>
@@ -13191,7 +13188,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>240</v>
       </c>
@@ -13238,7 +13235,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>241</v>
       </c>
@@ -13283,7 +13280,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>244</v>
       </c>
@@ -13330,7 +13327,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>245</v>
       </c>
@@ -13377,7 +13374,7 @@
         <v>100.93</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>246</v>
       </c>
@@ -13424,7 +13421,7 @@
         <v>90.1</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>251</v>
       </c>
@@ -13471,7 +13468,7 @@
         <v>96.08</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>252</v>
       </c>
@@ -13518,7 +13515,7 @@
         <v>99.58</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>254</v>
       </c>
@@ -13562,7 +13559,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>255</v>
       </c>
@@ -13607,7 +13604,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>255</v>
       </c>
@@ -13654,7 +13651,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>255</v>
       </c>
@@ -13701,7 +13698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>255</v>
       </c>
@@ -13748,7 +13745,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>255</v>
       </c>
@@ -13795,7 +13792,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>255</v>
       </c>
@@ -13842,7 +13839,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>255</v>
       </c>
@@ -13889,7 +13886,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>256</v>
       </c>
@@ -13936,7 +13933,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>260</v>
       </c>
@@ -13983,7 +13980,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>261</v>
       </c>
@@ -14030,7 +14027,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>262</v>
       </c>
@@ -14075,7 +14072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>263</v>
       </c>
@@ -14122,7 +14119,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>265</v>
       </c>
@@ -14169,7 +14166,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>266</v>
       </c>
@@ -14216,7 +14213,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>268</v>
       </c>
@@ -14263,7 +14260,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>269</v>
       </c>
@@ -14310,7 +14307,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>270</v>
       </c>
@@ -14357,7 +14354,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>271</v>
       </c>
@@ -14404,7 +14401,7 @@
         <v>23.85</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>272</v>
       </c>
@@ -14451,7 +14448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>273</v>
       </c>
@@ -14498,7 +14495,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>274</v>
       </c>
@@ -14545,7 +14542,7 @@
         <v>105.8</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>274</v>
       </c>
@@ -14592,7 +14589,7 @@
         <v>106.39</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>274</v>
       </c>
@@ -14639,7 +14636,7 @@
         <v>103.86</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>274</v>
       </c>
@@ -14686,7 +14683,7 @@
         <v>107.06</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>274</v>
       </c>
@@ -14733,7 +14730,7 @@
         <v>89.87</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>275</v>
       </c>
@@ -14780,7 +14777,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>275</v>
       </c>
@@ -14827,7 +14824,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>275</v>
       </c>
@@ -14874,7 +14871,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>275</v>
       </c>
@@ -14921,7 +14918,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>276</v>
       </c>
@@ -14968,7 +14965,7 @@
         <v>84.18</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>277</v>
       </c>
@@ -15015,7 +15012,7 @@
         <v>69.39</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>278</v>
       </c>
@@ -15062,7 +15059,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>278</v>
       </c>
@@ -15109,7 +15106,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>278</v>
       </c>
@@ -15156,7 +15153,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>278</v>
       </c>
@@ -15203,7 +15200,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>282</v>
       </c>
@@ -15250,7 +15247,7 @@
         <v>97.41</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>283</v>
       </c>
@@ -15297,7 +15294,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>285</v>
       </c>
@@ -15344,7 +15341,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>286</v>
       </c>
@@ -15391,7 +15388,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>286</v>
       </c>
@@ -15438,7 +15435,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>286</v>
       </c>
@@ -15485,7 +15482,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>286</v>
       </c>
@@ -15532,7 +15529,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>286</v>
       </c>
@@ -15579,7 +15576,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>288</v>
       </c>
@@ -15626,7 +15623,7 @@
         <v>185.71428571429001</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>290</v>
       </c>
@@ -15669,7 +15666,7 @@
         <v>88.89</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>290</v>
       </c>
@@ -15713,7 +15710,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>290</v>
       </c>
@@ -15757,7 +15754,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>290</v>
       </c>
@@ -15801,7 +15798,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>290</v>
       </c>
@@ -15845,7 +15842,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>290</v>
       </c>
@@ -15889,7 +15886,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>290</v>
       </c>
@@ -15933,7 +15930,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>290</v>
       </c>
@@ -15977,7 +15974,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>290</v>
       </c>
@@ -16021,7 +16018,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>290</v>
       </c>
@@ -16065,7 +16062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>292</v>
       </c>
@@ -16112,7 +16109,7 @@
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>292</v>
       </c>
@@ -16159,7 +16156,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>292</v>
       </c>
@@ -16206,7 +16203,7 @@
         <v>-17.68</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>292</v>
       </c>
@@ -16253,7 +16250,7 @@
         <v>126.45</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>294</v>
       </c>
@@ -16300,7 +16297,7 @@
         <v>-9.19</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>294</v>
       </c>
@@ -16347,7 +16344,7 @@
         <v>-0.82</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>294</v>
       </c>
@@ -16394,7 +16391,7 @@
         <v>-17.36</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>294</v>
       </c>
@@ -16441,7 +16438,7 @@
         <v>-22.99</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>300</v>
       </c>
@@ -16488,7 +16485,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>301</v>
       </c>
@@ -16535,7 +16532,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>302</v>
       </c>
@@ -16582,7 +16579,7 @@
         <v>21712</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>302</v>
       </c>
@@ -16629,7 +16626,7 @@
         <v>19569</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>302</v>
       </c>
@@ -16676,7 +16673,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>302</v>
       </c>
@@ -16723,7 +16720,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>302</v>
       </c>
@@ -16770,7 +16767,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>303</v>
       </c>
@@ -16817,7 +16814,7 @@
         <v>90.32</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>303</v>
       </c>
@@ -16864,7 +16861,7 @@
         <v>82.35</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>303</v>
       </c>
@@ -16911,7 +16908,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>303</v>
       </c>
@@ -16958,7 +16955,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>304</v>
       </c>
@@ -17005,7 +17002,7 @@
         <v>98.47</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>306</v>
       </c>
@@ -17052,7 +17049,7 @@
         <v>105.83</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>306</v>
       </c>
@@ -17099,7 +17096,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>306</v>
       </c>
@@ -17146,7 +17143,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>306</v>
       </c>
@@ -17193,7 +17190,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>306</v>
       </c>
@@ -17240,7 +17237,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>306</v>
       </c>
@@ -17287,7 +17284,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>306</v>
       </c>
@@ -17334,7 +17331,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>318</v>
       </c>
@@ -17381,7 +17378,7 @@
         <v>90.28</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>323</v>
       </c>
@@ -17428,7 +17425,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>324</v>
       </c>
@@ -17475,7 +17472,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>325</v>
       </c>
@@ -17522,7 +17519,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>326</v>
       </c>
@@ -17569,7 +17566,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>327</v>
       </c>
@@ -17616,7 +17613,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>332</v>
       </c>
@@ -17663,7 +17660,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>334</v>
       </c>
@@ -17710,7 +17707,7 @@
         <v>88.84</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>336</v>
       </c>
@@ -17757,7 +17754,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>337</v>
       </c>
@@ -17804,7 +17801,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>338</v>
       </c>
@@ -17851,7 +17848,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>339</v>
       </c>
@@ -17898,7 +17895,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>341</v>
       </c>
@@ -17945,7 +17942,7 @@
         <v>102.25</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>344</v>
       </c>
@@ -17992,7 +17989,7 @@
         <v>99.43</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>346</v>
       </c>
@@ -18039,7 +18036,7 @@
         <v>91.88</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>347</v>
       </c>
@@ -18086,7 +18083,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>348</v>
       </c>
@@ -18133,7 +18130,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>351</v>
       </c>
@@ -18178,7 +18175,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>352</v>
       </c>
@@ -18223,7 +18220,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>355</v>
       </c>
@@ -18270,7 +18267,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>356</v>
       </c>
@@ -18317,7 +18314,7 @@
         <v>49.14</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>357</v>
       </c>
@@ -18362,7 +18359,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>358</v>
       </c>
@@ -18409,7 +18406,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>359</v>
       </c>
@@ -18456,7 +18453,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>361</v>
       </c>
@@ -18503,7 +18500,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>362</v>
       </c>
@@ -18550,7 +18547,7 @@
         <v>99.63</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>362</v>
       </c>
@@ -18597,7 +18594,7 @@
         <v>99.72</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>362</v>
       </c>
@@ -18644,7 +18641,7 @@
         <v>98.64</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>363</v>
       </c>
@@ -18691,7 +18688,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>364</v>
       </c>
@@ -18738,7 +18735,7 @@
         <v>93.89</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>366</v>
       </c>
@@ -18785,7 +18782,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>367</v>
       </c>
@@ -18832,7 +18829,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>368</v>
       </c>
@@ -18879,7 +18876,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>369</v>
       </c>
@@ -18926,7 +18923,7 @@
         <v>88.89</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>369</v>
       </c>
@@ -18973,7 +18970,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>369</v>
       </c>
@@ -19020,7 +19017,7 @@
         <v>90.14</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>371</v>
       </c>
@@ -19067,7 +19064,7 @@
         <v>73.69</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>372</v>
       </c>
@@ -19114,7 +19111,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>373</v>
       </c>
@@ -19161,7 +19158,7 @@
         <v>96.32</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>373</v>
       </c>
@@ -19208,7 +19205,7 @@
         <v>96.7</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>373</v>
       </c>
@@ -19255,7 +19252,7 @@
         <v>97.75</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>373</v>
       </c>
@@ -19302,7 +19299,7 @@
         <v>94.51</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>373</v>
       </c>
@@ -19349,7 +19346,7 @@
         <v>94.44</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>373</v>
       </c>
@@ -19396,7 +19393,7 @@
         <v>96.74</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>373</v>
       </c>
@@ -19443,7 +19440,7 @@
         <v>97.75</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>375</v>
       </c>
@@ -19490,7 +19487,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>375</v>
       </c>
@@ -19537,7 +19534,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>375</v>
       </c>
@@ -19584,7 +19581,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>376</v>
       </c>
@@ -19631,7 +19628,7 @@
         <v>117.87</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>377</v>
       </c>
@@ -19678,7 +19675,7 @@
         <v>125.01</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>379</v>
       </c>
@@ -19725,7 +19722,7 @@
         <v>104.11</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>381</v>
       </c>
@@ -19772,7 +19769,7 @@
         <v>98.22</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>382</v>
       </c>
@@ -19819,7 +19816,7 @@
         <v>99.85</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>383</v>
       </c>
@@ -19866,7 +19863,7 @@
         <v>136.96</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>384</v>
       </c>
@@ -19913,7 +19910,7 @@
         <v>103.23</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>385</v>
       </c>
@@ -19960,7 +19957,7 @@
         <v>118.92</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>386</v>
       </c>
@@ -20007,7 +20004,7 @@
         <v>118.92</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>386</v>
       </c>
@@ -20054,7 +20051,7 @@
         <v>116.84</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>386</v>
       </c>
@@ -20101,7 +20098,7 @@
         <v>126.48</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>386</v>
       </c>
@@ -20148,7 +20145,7 @@
         <v>112.99</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>389</v>
       </c>
@@ -20191,7 +20188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>389</v>
       </c>
@@ -20235,7 +20232,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>389</v>
       </c>
@@ -20279,7 +20276,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>389</v>
       </c>
@@ -20323,7 +20320,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>389</v>
       </c>
@@ -20367,7 +20364,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>389</v>
       </c>
@@ -20411,7 +20408,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>389</v>
       </c>
@@ -20455,7 +20452,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>389</v>
       </c>
@@ -20499,7 +20496,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>389</v>
       </c>
@@ -20543,7 +20540,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>389</v>
       </c>
@@ -20587,7 +20584,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>389</v>
       </c>
@@ -20631,7 +20628,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>389</v>
       </c>
@@ -20675,7 +20672,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>389</v>
       </c>
@@ -20719,7 +20716,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>390</v>
       </c>
@@ -20766,7 +20763,7 @@
         <v>101.17</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>390</v>
       </c>
@@ -20813,7 +20810,7 @@
         <v>98.8</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>390</v>
       </c>
@@ -20860,7 +20857,7 @@
         <v>96.43</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>390</v>
       </c>
@@ -20907,7 +20904,7 @@
         <v>115.12</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>390</v>
       </c>
@@ -20954,7 +20951,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>390</v>
       </c>
@@ -21001,7 +20998,7 @@
         <v>101.22</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>390</v>
       </c>
@@ -21048,7 +21045,7 @@
         <v>104.4</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>390</v>
       </c>
@@ -21095,7 +21092,7 @@
         <v>105.68</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>390</v>
       </c>
@@ -21142,7 +21139,7 @@
         <v>95.51</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>390</v>
       </c>
@@ -21189,7 +21186,7 @@
         <v>95.51</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>390</v>
       </c>
@@ -21236,7 +21233,7 @@
         <v>101.12</v>
       </c>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>390</v>
       </c>
@@ -21283,7 +21280,7 @@
         <v>99.17</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>390</v>
       </c>
@@ -21330,7 +21327,7 @@
         <v>101.12</v>
       </c>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>392</v>
       </c>
@@ -21377,7 +21374,7 @@
         <v>145.21</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>393</v>
       </c>
@@ -21422,7 +21419,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>394</v>
       </c>
@@ -21469,7 +21466,7 @@
         <v>91.71</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>395</v>
       </c>
@@ -21516,7 +21513,7 @@
         <v>187.27</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>397</v>
       </c>
@@ -21563,7 +21560,7 @@
         <v>95.26</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>398</v>
       </c>
@@ -21610,7 +21607,7 @@
         <v>159.5</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>399</v>
       </c>
@@ -21657,7 +21654,7 @@
         <v>102.93</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>400</v>
       </c>
@@ -21704,7 +21701,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>401</v>
       </c>
@@ -21751,7 +21748,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>402</v>
       </c>
@@ -21796,7 +21793,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>403</v>
       </c>
@@ -21843,7 +21840,7 @@
         <v>14410</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>408</v>
       </c>
@@ -21890,7 +21887,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>408</v>
       </c>
@@ -21937,7 +21934,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>408</v>
       </c>
@@ -21984,7 +21981,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>408</v>
       </c>
@@ -22031,7 +22028,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>409</v>
       </c>
@@ -22074,7 +22071,7 @@
       <c r="N387" s="3"/>
       <c r="O387" s="3"/>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>409</v>
       </c>
@@ -22121,7 +22118,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>409</v>
       </c>
@@ -22168,7 +22165,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>413</v>
       </c>
@@ -22215,7 +22212,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
         <v>414</v>
       </c>
@@ -22262,7 +22259,7 @@
         <v>93.6</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>414</v>
       </c>
@@ -22309,7 +22306,7 @@
         <v>91.84</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>414</v>
       </c>
@@ -22356,7 +22353,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>414</v>
       </c>
@@ -22403,7 +22400,7 @@
         <v>87.78</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>414</v>
       </c>
@@ -22450,7 +22447,7 @@
         <v>102.04</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>414</v>
       </c>
@@ -22497,7 +22494,7 @@
         <v>99.89</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>414</v>
       </c>
@@ -22544,7 +22541,7 @@
         <v>77.78</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>414</v>
       </c>
@@ -22591,7 +22588,7 @@
         <v>105.26</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>414</v>
       </c>
@@ -22638,7 +22635,7 @@
         <v>93.1</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>414</v>
       </c>
@@ -22685,7 +22682,7 @@
         <v>92.68</v>
       </c>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>415</v>
       </c>
@@ -22732,7 +22729,7 @@
         <v>95.56</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>415</v>
       </c>
@@ -22779,7 +22776,7 @@
         <v>98.9</v>
       </c>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>415</v>
       </c>
@@ -22826,7 +22823,7 @@
         <v>89.8</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>415</v>
       </c>
@@ -22873,7 +22870,7 @@
         <v>86.17</v>
       </c>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>415</v>
       </c>
@@ -22920,7 +22917,7 @@
         <v>119.61</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>415</v>
       </c>
@@ -22967,7 +22964,7 @@
         <v>98.92</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>415</v>
       </c>
@@ -23014,7 +23011,7 @@
         <v>101.11</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>415</v>
       </c>
@@ -23061,7 +23058,7 @@
         <v>82.47</v>
       </c>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>415</v>
       </c>
@@ -23108,7 +23105,7 @@
         <v>90.43</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>415</v>
       </c>
@@ -23155,7 +23152,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>415</v>
       </c>
@@ -23202,7 +23199,7 @@
         <v>90.32</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>415</v>
       </c>
@@ -23249,7 +23246,7 @@
         <v>102.06</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>415</v>
       </c>
@@ -23296,7 +23293,7 @@
         <v>94.68</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>415</v>
       </c>
@@ -23343,7 +23340,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>415</v>
       </c>
@@ -23390,7 +23387,7 @@
         <v>91.75</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
         <v>416</v>
       </c>
@@ -23437,7 +23434,7 @@
         <v>96.48</v>
       </c>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>416</v>
       </c>
@@ -23484,7 +23481,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>416</v>
       </c>
@@ -23531,7 +23528,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>416</v>
       </c>
@@ -23578,7 +23575,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>416</v>
       </c>
@@ -23625,7 +23622,7 @@
         <v>105.26</v>
       </c>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>416</v>
       </c>
@@ -23672,7 +23669,7 @@
         <v>87.63</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>416</v>
       </c>
@@ -23719,7 +23716,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
         <v>417</v>
       </c>
@@ -23766,7 +23763,7 @@
         <v>99.34</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>417</v>
       </c>
@@ -23813,7 +23810,7 @@
         <v>98.95</v>
       </c>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>417</v>
       </c>
@@ -23860,7 +23857,7 @@
         <v>82.61</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>417</v>
       </c>
@@ -23907,7 +23904,7 @@
         <v>104.44</v>
       </c>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>417</v>
       </c>
@@ -23954,7 +23951,7 @@
         <v>101.12</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>417</v>
       </c>
@@ -24001,7 +23998,7 @@
         <v>104.26</v>
       </c>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>417</v>
       </c>
@@ -24048,7 +24045,7 @@
         <v>104.65</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
         <v>418</v>
       </c>
@@ -24095,7 +24092,7 @@
         <v>93.96</v>
       </c>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>418</v>
       </c>
@@ -24142,7 +24139,7 @@
         <v>107.23</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>418</v>
       </c>
@@ -24189,7 +24186,7 @@
         <v>81.52</v>
       </c>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>418</v>
       </c>
@@ -24236,7 +24233,7 @@
         <v>91.75</v>
       </c>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>418</v>
       </c>
@@ -24283,7 +24280,7 @@
         <v>101.1</v>
       </c>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>418</v>
       </c>
@@ -24330,7 +24327,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>418</v>
       </c>
@@ -24377,7 +24374,7 @@
         <v>81.52</v>
       </c>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>418</v>
       </c>
@@ -24424,7 +24421,7 @@
         <v>90.72</v>
       </c>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>418</v>
       </c>
@@ -24471,7 +24468,7 @@
         <v>96.84</v>
       </c>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>418</v>
       </c>
@@ -24518,7 +24515,7 @@
         <v>101.03</v>
       </c>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="1">
         <v>420</v>
       </c>
@@ -24565,7 +24562,7 @@
         <v>100.3</v>
       </c>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>420</v>
       </c>
@@ -24612,7 +24609,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>420</v>
       </c>
@@ -24659,7 +24656,7 @@
         <v>127.27</v>
       </c>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>420</v>
       </c>
@@ -24706,7 +24703,7 @@
         <v>97.83</v>
       </c>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>420</v>
       </c>
@@ -24753,7 +24750,7 @@
         <v>84.88</v>
       </c>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>420</v>
       </c>
@@ -24800,7 +24797,7 @@
         <v>95.79</v>
       </c>
     </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>420</v>
       </c>
@@ -24847,7 +24844,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
         <v>422</v>
       </c>
@@ -24894,7 +24891,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="1">
         <v>423</v>
       </c>
@@ -24941,7 +24938,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="1">
         <v>424</v>
       </c>
@@ -25029,7 +25026,7 @@
       <c r="N450" s="3"/>
       <c r="O450" s="3"/>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="1">
         <v>427</v>
       </c>
@@ -25076,7 +25073,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>427</v>
       </c>
@@ -25123,7 +25120,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>427</v>
       </c>
@@ -25170,7 +25167,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>427</v>
       </c>
@@ -25217,7 +25214,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>427</v>
       </c>
@@ -25264,7 +25261,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>427</v>
       </c>
@@ -25309,7 +25306,7 @@
       </c>
       <c r="O456" s="3"/>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>427</v>
       </c>
@@ -25356,7 +25353,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="1">
         <v>428</v>
       </c>
@@ -25403,7 +25400,7 @@
         <v>15.12</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>428</v>
       </c>
@@ -25450,7 +25447,7 @@
         <v>20.260000000000002</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>428</v>
       </c>
@@ -25497,7 +25494,7 @@
         <v>17.59</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>428</v>
       </c>
@@ -25544,7 +25541,7 @@
         <v>86.33</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>428</v>
       </c>
@@ -25591,7 +25588,7 @@
         <v>7.27</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>428</v>
       </c>
@@ -25638,7 +25635,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>428</v>
       </c>
@@ -25685,7 +25682,7 @@
         <v>171.7</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>428</v>
       </c>
@@ -25725,7 +25722,7 @@
       <c r="N465" s="3"/>
       <c r="O465" s="3"/>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>429</v>
       </c>
@@ -25772,7 +25769,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>429</v>
       </c>
@@ -25819,7 +25816,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>429</v>
       </c>
@@ -25866,7 +25863,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>429</v>
       </c>
@@ -25913,7 +25910,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>429</v>
       </c>
@@ -25960,7 +25957,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>429</v>
       </c>
@@ -26007,7 +26004,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>429</v>
       </c>
@@ -26054,7 +26051,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="1">
         <v>430</v>
       </c>
@@ -26101,7 +26098,7 @@
         <v>110.79</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>430</v>
       </c>
@@ -26148,7 +26145,7 @@
         <v>105.86</v>
       </c>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>430</v>
       </c>
@@ -26195,7 +26192,7 @@
         <v>140.35</v>
       </c>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>430</v>
       </c>
@@ -26242,7 +26239,7 @@
         <v>104.01</v>
       </c>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>430</v>
       </c>
@@ -26289,7 +26286,7 @@
         <v>106.55</v>
       </c>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="1">
         <v>431</v>
       </c>
@@ -26336,7 +26333,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="1">
         <v>432</v>
       </c>
@@ -26383,7 +26380,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>432</v>
       </c>
@@ -26430,7 +26427,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>432</v>
       </c>
@@ -26477,7 +26474,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>432</v>
       </c>
@@ -26524,7 +26521,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>432</v>
       </c>
@@ -26571,7 +26568,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>432</v>
       </c>
@@ -26618,7 +26615,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>432</v>
       </c>
@@ -26665,7 +26662,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>432</v>
       </c>
@@ -26712,7 +26709,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>432</v>
       </c>
@@ -26759,7 +26756,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>432</v>
       </c>
@@ -26806,7 +26803,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="1">
         <v>433</v>
       </c>
@@ -26853,7 +26850,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>433</v>
       </c>
@@ -26900,7 +26897,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>433</v>
       </c>
@@ -26947,7 +26944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>433</v>
       </c>
@@ -26994,7 +26991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>433</v>
       </c>
@@ -27041,7 +27038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>433</v>
       </c>
@@ -27088,7 +27085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>433</v>
       </c>
@@ -27133,7 +27130,7 @@
       </c>
       <c r="O495" s="3"/>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>433</v>
       </c>
@@ -27173,7 +27170,7 @@
       <c r="N496" s="3"/>
       <c r="O496" s="3"/>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="1">
         <v>434</v>
       </c>
@@ -27216,7 +27213,7 @@
       <c r="N497" s="3"/>
       <c r="O497" s="3"/>
     </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>434</v>
       </c>
@@ -27263,7 +27260,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>434</v>
       </c>
@@ -27310,7 +27307,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>434</v>
       </c>
@@ -27357,7 +27354,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>434</v>
       </c>
@@ -27404,7 +27401,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>434</v>
       </c>
@@ -27451,7 +27448,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>434</v>
       </c>
@@ -27498,7 +27495,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>435</v>
       </c>
@@ -27545,7 +27542,7 @@
         <v>96.09</v>
       </c>
     </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>435</v>
       </c>
@@ -27592,7 +27589,7 @@
         <v>66.67</v>
       </c>
     </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>435</v>
       </c>
@@ -27639,7 +27636,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>435</v>
       </c>
@@ -27686,7 +27683,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>435</v>
       </c>
@@ -27733,7 +27730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>435</v>
       </c>
@@ -27780,7 +27777,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>435</v>
       </c>
@@ -27827,7 +27824,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="1">
         <v>436</v>
       </c>
@@ -27874,7 +27871,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>436</v>
       </c>
@@ -27921,7 +27918,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>436</v>
       </c>
@@ -27968,7 +27965,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="1">
         <v>437</v>
       </c>
@@ -28015,7 +28012,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="1">
         <v>439</v>
       </c>
@@ -28062,7 +28059,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>439</v>
       </c>
@@ -28109,7 +28106,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>439</v>
       </c>
@@ -28156,7 +28153,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="1">
         <v>440</v>
       </c>
@@ -28203,7 +28200,7 @@
         <v>99.77</v>
       </c>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>440</v>
       </c>
@@ -28250,7 +28247,7 @@
         <v>99.81</v>
       </c>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>440</v>
       </c>
@@ -28297,7 +28294,7 @@
         <v>99.25</v>
       </c>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="1">
         <v>444</v>
       </c>
@@ -28344,7 +28341,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="1">
         <v>445</v>
       </c>
@@ -28391,7 +28388,7 @@
         <v>75.7</v>
       </c>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="1">
         <v>447</v>
       </c>
@@ -28438,7 +28435,7 @@
         <v>16.54</v>
       </c>
     </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="1">
         <v>448</v>
       </c>
@@ -28485,7 +28482,7 @@
         <v>39.619999999999997</v>
       </c>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="1">
         <v>451</v>
       </c>
@@ -28532,7 +28529,7 @@
         <v>119.5</v>
       </c>
     </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="1">
         <v>452</v>
       </c>
@@ -28579,7 +28576,7 @@
         <v>102.27</v>
       </c>
     </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="1">
         <v>453</v>
       </c>
@@ -28626,7 +28623,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="1">
         <v>455</v>
       </c>
@@ -29049,7 +29046,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="537" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="1">
         <v>460</v>
       </c>
@@ -29096,7 +29093,7 @@
         <v>91.439688715953309</v>
       </c>
     </row>
-    <row r="538" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="1">
         <v>466</v>
       </c>
@@ -29143,7 +29140,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="539" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="1">
         <v>467</v>
       </c>
@@ -29190,7 +29187,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="540" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="1">
         <v>468</v>
       </c>
@@ -29237,7 +29234,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="541" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="1">
         <v>469</v>
       </c>
@@ -29284,7 +29281,7 @@
         <v>92.65</v>
       </c>
     </row>
-    <row r="542" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>469</v>
       </c>
@@ -29331,7 +29328,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="543" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>469</v>
       </c>
@@ -29378,7 +29375,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="544" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>469</v>
       </c>
@@ -29425,7 +29422,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="545" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>469</v>
       </c>
@@ -29472,7 +29469,7 @@
         <v>96.39</v>
       </c>
     </row>
-    <row r="546" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>469</v>
       </c>
@@ -29519,7 +29516,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="547" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>469</v>
       </c>
@@ -29566,7 +29563,7 @@
         <v>107.69</v>
       </c>
     </row>
-    <row r="548" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>469</v>
       </c>
@@ -29613,7 +29610,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="549" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>469</v>
       </c>
@@ -29660,7 +29657,7 @@
         <v>87.64</v>
       </c>
     </row>
-    <row r="550" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550">
         <v>469</v>
       </c>
@@ -29707,7 +29704,7 @@
         <v>65.22</v>
       </c>
     </row>
-    <row r="551" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>469</v>
       </c>
@@ -29754,7 +29751,7 @@
         <v>84.27</v>
       </c>
     </row>
-    <row r="552" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="1">
         <v>470</v>
       </c>
@@ -29801,7 +29798,7 @@
         <v>105.6</v>
       </c>
     </row>
-    <row r="553" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>470</v>
       </c>
@@ -29848,7 +29845,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="554" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>470</v>
       </c>
@@ -29895,7 +29892,7 @@
         <v>115.29</v>
       </c>
     </row>
-    <row r="555" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>470</v>
       </c>
@@ -29942,7 +29939,7 @@
         <v>106.38</v>
       </c>
     </row>
-    <row r="556" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>470</v>
       </c>
@@ -29989,7 +29986,7 @@
         <v>103.09</v>
       </c>
     </row>
-    <row r="557" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>470</v>
       </c>
@@ -30036,7 +30033,7 @@
         <v>103.23</v>
       </c>
     </row>
-    <row r="558" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="1">
         <v>471</v>
       </c>
@@ -30083,7 +30080,7 @@
         <v>98.93</v>
       </c>
     </row>
-    <row r="559" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>471</v>
       </c>
@@ -30130,7 +30127,7 @@
         <v>93.55</v>
       </c>
     </row>
-    <row r="560" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>471</v>
       </c>
@@ -30177,7 +30174,7 @@
         <v>106.59</v>
       </c>
     </row>
-    <row r="561" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>471</v>
       </c>
@@ -30224,7 +30221,7 @@
         <v>120.48</v>
       </c>
     </row>
-    <row r="562" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>471</v>
       </c>
@@ -30271,7 +30268,7 @@
         <v>102.13</v>
       </c>
     </row>
-    <row r="563" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>471</v>
       </c>
@@ -30318,7 +30315,7 @@
         <v>73.680000000000007</v>
       </c>
     </row>
-    <row r="564" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>471</v>
       </c>
@@ -30365,7 +30362,7 @@
         <v>113.95</v>
       </c>
     </row>
-    <row r="565" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565">
         <v>471</v>
       </c>
@@ -30412,7 +30409,7 @@
         <v>82.11</v>
       </c>
     </row>
-    <row r="566" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>473</v>
       </c>
@@ -30459,7 +30456,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="567" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>473</v>
       </c>
@@ -30506,7 +30503,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="568" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>473</v>
       </c>
@@ -30553,7 +30550,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="569" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>473</v>
       </c>
@@ -30600,7 +30597,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="570" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="1">
         <v>474</v>
       </c>
@@ -30643,7 +30640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>474</v>
       </c>
@@ -30687,7 +30684,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="572" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>474</v>
       </c>
@@ -30731,7 +30728,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="573" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>474</v>
       </c>
@@ -30775,7 +30772,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="574" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574">
         <v>474</v>
       </c>
@@ -30819,7 +30816,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="575" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>474</v>
       </c>
@@ -30863,7 +30860,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="576" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>474</v>
       </c>
@@ -30907,7 +30904,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="577" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>474</v>
       </c>
@@ -30951,7 +30948,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="578" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>474</v>
       </c>
@@ -30995,7 +30992,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="579" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>474</v>
       </c>
@@ -31039,7 +31036,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="580" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>474</v>
       </c>
@@ -31083,7 +31080,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="581" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>474</v>
       </c>
@@ -31127,7 +31124,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="582" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>474</v>
       </c>
@@ -31171,7 +31168,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="583" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>475</v>
       </c>
@@ -31218,7 +31215,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="584" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>476</v>
       </c>
@@ -31265,7 +31262,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="585" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585">
         <v>476</v>
       </c>
@@ -31312,7 +31309,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="586" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586">
         <v>476</v>
       </c>
@@ -31359,7 +31356,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="587" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587">
         <v>476</v>
       </c>
@@ -31406,7 +31403,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="588" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="1">
         <v>477</v>
       </c>
@@ -31447,7 +31444,7 @@
       <c r="N588" s="3"/>
       <c r="O588" s="3"/>
     </row>
-    <row r="589" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>477</v>
       </c>
@@ -31491,7 +31488,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="590" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>477</v>
       </c>
@@ -31535,7 +31532,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="591" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>477</v>
       </c>
@@ -31579,7 +31576,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="592" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>477</v>
       </c>
@@ -31623,7 +31620,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="593" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>477</v>
       </c>
@@ -31667,7 +31664,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="594" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>477</v>
       </c>
@@ -31711,7 +31708,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="595" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595">
         <v>477</v>
       </c>
@@ -31755,7 +31752,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="596" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596">
         <v>477</v>
       </c>
@@ -31799,7 +31796,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="597" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597">
         <v>477</v>
       </c>
@@ -31843,7 +31840,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="598" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598">
         <v>477</v>
       </c>
@@ -31887,7 +31884,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="599" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599">
         <v>477</v>
       </c>
@@ -31931,7 +31928,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="600" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600">
         <v>477</v>
       </c>
@@ -31975,7 +31972,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="601" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>478</v>
       </c>
@@ -32018,7 +32015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602">
         <v>478</v>
       </c>
@@ -32062,7 +32059,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="603" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>478</v>
       </c>
@@ -32106,7 +32103,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="604" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>478</v>
       </c>
@@ -32150,7 +32147,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="605" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>478</v>
       </c>
@@ -32194,7 +32191,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="606" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>478</v>
       </c>
@@ -32238,7 +32235,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="607" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>478</v>
       </c>
@@ -32282,7 +32279,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="608" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>478</v>
       </c>
@@ -32326,7 +32323,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="609" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>478</v>
       </c>
@@ -32370,7 +32367,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="610" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>478</v>
       </c>
@@ -32414,7 +32411,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="611" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611">
         <v>478</v>
       </c>
@@ -32458,7 +32455,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="612" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612">
         <v>478</v>
       </c>
@@ -32502,7 +32499,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="613" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613">
         <v>478</v>
       </c>
@@ -32546,7 +32543,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="614" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="1">
         <v>479</v>
       </c>
@@ -32589,7 +32586,7 @@
       <c r="N614" s="3"/>
       <c r="O614" s="3"/>
     </row>
-    <row r="615" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>479</v>
       </c>
@@ -32636,7 +32633,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="616" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>479</v>
       </c>
@@ -32683,7 +32680,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="617" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>479</v>
       </c>
@@ -32730,7 +32727,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="618" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>479</v>
       </c>
@@ -32777,7 +32774,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="619" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>479</v>
       </c>
@@ -32824,7 +32821,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="620" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>479</v>
       </c>
@@ -32871,7 +32868,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="621" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>479</v>
       </c>
@@ -32918,7 +32915,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="622" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622">
         <v>479</v>
       </c>
@@ -32965,7 +32962,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="623" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623">
         <v>479</v>
       </c>
@@ -33012,7 +33009,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="624" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624">
         <v>479</v>
       </c>
@@ -33059,7 +33056,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="625" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625">
         <v>479</v>
       </c>
@@ -33106,7 +33103,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="626" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626">
         <v>479</v>
       </c>
@@ -33153,7 +33150,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>480</v>
       </c>
@@ -33196,7 +33193,7 @@
       <c r="N627" s="3"/>
       <c r="O627" s="3"/>
     </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628">
         <v>480</v>
       </c>
@@ -33243,7 +33240,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629">
         <v>480</v>
       </c>
@@ -33290,7 +33287,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630">
         <v>480</v>
       </c>
@@ -33337,7 +33334,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="631" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>480</v>
       </c>
@@ -33384,7 +33381,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>480</v>
       </c>
@@ -33431,7 +33428,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="633" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>480</v>
       </c>
@@ -33478,7 +33475,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>480</v>
       </c>
@@ -33525,7 +33522,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="635" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>480</v>
       </c>
@@ -33572,7 +33569,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>480</v>
       </c>
@@ -33619,7 +33616,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637">
         <v>480</v>
       </c>
@@ -33666,7 +33663,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638">
         <v>480</v>
       </c>
@@ -33713,7 +33710,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639">
         <v>480</v>
       </c>
@@ -33760,7 +33757,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>481</v>
       </c>
@@ -33807,7 +33804,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="641" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641">
         <v>481</v>
       </c>
@@ -33849,7 +33846,7 @@
       </c>
       <c r="O641" s="3"/>
     </row>
-    <row r="642" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>484</v>
       </c>
@@ -33896,7 +33893,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="643" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>485</v>
       </c>
@@ -33937,7 +33934,7 @@
       <c r="N643" s="3"/>
       <c r="O643" s="3"/>
     </row>
-    <row r="644" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>485</v>
       </c>
@@ -33981,7 +33978,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="645" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>485</v>
       </c>
@@ -34025,7 +34022,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>485</v>
       </c>
@@ -34069,7 +34066,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="647" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>485</v>
       </c>
@@ -34113,7 +34110,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="648" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>485</v>
       </c>
@@ -34157,7 +34154,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="649" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>485</v>
       </c>
@@ -34201,7 +34198,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="650" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650">
         <v>485</v>
       </c>
@@ -34245,7 +34242,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="651" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>485</v>
       </c>
@@ -34289,7 +34286,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="652" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>485</v>
       </c>
@@ -34380,7 +34377,7 @@
         <v>2890610</v>
       </c>
     </row>
-    <row r="654" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" s="1">
         <v>487</v>
       </c>
@@ -34427,7 +34424,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="655" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" s="1">
         <v>488</v>
       </c>
@@ -34470,7 +34467,7 @@
         <v>72.16</v>
       </c>
     </row>
-    <row r="656" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>488</v>
       </c>
@@ -34514,7 +34511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="657" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>488</v>
       </c>
@@ -34558,7 +34555,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="658" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>488</v>
       </c>
@@ -34602,7 +34599,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="659" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>488</v>
       </c>
@@ -34646,7 +34643,7 @@
         <v>96.55</v>
       </c>
     </row>
-    <row r="660" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>488</v>
       </c>
@@ -34690,7 +34687,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="661" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>488</v>
       </c>
@@ -34734,7 +34731,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="662" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>488</v>
       </c>
@@ -34778,7 +34775,7 @@
         <v>57.14</v>
       </c>
     </row>
-    <row r="663" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663">
         <v>488</v>
       </c>
@@ -34822,7 +34819,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="664" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664">
         <v>488</v>
       </c>
@@ -34866,7 +34863,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="665" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>490</v>
       </c>
@@ -34913,7 +34910,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="666" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" s="1">
         <v>491</v>
       </c>
@@ -34960,7 +34957,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="667" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" s="1">
         <v>492</v>
       </c>
@@ -35007,7 +35004,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="668" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>493</v>
       </c>
@@ -35054,7 +35051,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="669" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" s="1">
         <v>494</v>
       </c>
@@ -35101,7 +35098,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="670" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" s="1">
         <v>495</v>
       </c>
@@ -35148,7 +35145,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="671" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" s="1">
         <v>496</v>
       </c>
@@ -35195,7 +35192,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="672" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" s="1">
         <v>498</v>
       </c>
@@ -35242,7 +35239,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="673" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" s="1">
         <v>499</v>
       </c>
@@ -35289,7 +35286,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="674" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" s="1">
         <v>500</v>
       </c>
@@ -35336,7 +35333,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="675" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" s="1">
         <v>501</v>
       </c>
@@ -35383,7 +35380,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="676" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" s="1">
         <v>502</v>
       </c>
@@ -35430,7 +35427,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="677" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" s="1">
         <v>503</v>
       </c>
@@ -35477,7 +35474,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="678" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>504</v>
       </c>
@@ -35524,7 +35521,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="679" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" s="1">
         <v>505</v>
       </c>
@@ -35571,7 +35568,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="680" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" s="1">
         <v>506</v>
       </c>
@@ -35618,7 +35615,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="681" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" s="1">
         <v>507</v>
       </c>
@@ -35665,7 +35662,7 @@
         <v>98.75</v>
       </c>
     </row>
-    <row r="682" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" s="1">
         <v>508</v>
       </c>
@@ -35712,7 +35709,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="683" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" s="1">
         <v>509</v>
       </c>
@@ -35753,7 +35750,7 @@
       <c r="N683" s="3"/>
       <c r="O683" s="3"/>
     </row>
-    <row r="684" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>509</v>
       </c>
@@ -35797,7 +35794,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="685" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>509</v>
       </c>
@@ -35841,7 +35838,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="686" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>509</v>
       </c>
@@ -35885,7 +35882,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="687" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>509</v>
       </c>
@@ -35929,7 +35926,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="688" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>509</v>
       </c>
@@ -35973,7 +35970,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="689" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>509</v>
       </c>
@@ -36017,7 +36014,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="690" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>509</v>
       </c>
@@ -36061,7 +36058,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="691" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>509</v>
       </c>
@@ -36105,7 +36102,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="692" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>509</v>
       </c>
@@ -36149,7 +36146,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="693" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693">
         <v>509</v>
       </c>
@@ -36193,7 +36190,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="694" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>509</v>
       </c>
@@ -36237,7 +36234,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="695" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>509</v>
       </c>
@@ -36281,7 +36278,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="696" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>509</v>
       </c>
@@ -36325,7 +36322,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="697" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>509</v>
       </c>
@@ -36369,7 +36366,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="698" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>509</v>
       </c>
@@ -36413,7 +36410,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="699" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699">
         <v>509</v>
       </c>
@@ -36457,7 +36454,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="700" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700">
         <v>509</v>
       </c>
@@ -36501,7 +36498,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="701" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701">
         <v>509</v>
       </c>
@@ -36545,7 +36542,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="702" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" s="1">
         <v>510</v>
       </c>
@@ -36592,7 +36589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703">
         <v>510</v>
       </c>
@@ -36637,7 +36634,7 @@
       </c>
       <c r="O703" s="3"/>
     </row>
-    <row r="704" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" s="1">
         <v>511</v>
       </c>
@@ -36684,7 +36681,7 @@
         <v>86.36</v>
       </c>
     </row>
-    <row r="705" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705">
         <v>511</v>
       </c>
@@ -36731,7 +36728,7 @@
         <v>80.849999999999994</v>
       </c>
     </row>
-    <row r="706" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706">
         <v>511</v>
       </c>
@@ -36778,7 +36775,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="707" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707">
         <v>511</v>
       </c>
@@ -36825,7 +36822,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="708" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708">
         <v>511</v>
       </c>
@@ -36872,7 +36869,7 @@
         <v>92.86</v>
       </c>
     </row>
-    <row r="709" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709">
         <v>511</v>
       </c>
@@ -36919,7 +36916,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="710" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710">
         <v>511</v>
       </c>
@@ -36966,7 +36963,7 @@
         <v>82.32</v>
       </c>
     </row>
-    <row r="711" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711">
         <v>511</v>
       </c>
@@ -37013,7 +37010,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="712" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712" s="1">
         <v>513</v>
       </c>
@@ -37060,7 +37057,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="713" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713" s="1">
         <v>514</v>
       </c>
@@ -37107,7 +37104,7 @@
         <v>91.82</v>
       </c>
     </row>
-    <row r="714" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714" s="1">
         <v>515</v>
       </c>
@@ -37152,7 +37149,7 @@
       </c>
       <c r="O714" s="3"/>
     </row>
-    <row r="715" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715" s="1">
         <v>516</v>
       </c>
@@ -37197,7 +37194,7 @@
       </c>
       <c r="O715" s="3"/>
     </row>
-    <row r="716" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716" s="1">
         <v>518</v>
       </c>
@@ -37241,7 +37238,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="717" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>519</v>
       </c>
@@ -37288,7 +37285,7 @@
         <v>431.45</v>
       </c>
     </row>
-    <row r="718" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718">
         <v>519</v>
       </c>
@@ -37335,7 +37332,7 @@
         <v>112.9</v>
       </c>
     </row>
-    <row r="719" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719">
         <v>519</v>
       </c>
@@ -37382,7 +37379,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="720" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720" s="1">
         <v>522</v>
       </c>
@@ -37427,7 +37424,7 @@
       </c>
       <c r="O720" s="3"/>
     </row>
-    <row r="721" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721" s="1">
         <v>523</v>
       </c>
@@ -37474,7 +37471,7 @@
         <v>125.74</v>
       </c>
     </row>
-    <row r="722" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722">
         <v>523</v>
       </c>
@@ -37521,7 +37518,7 @@
         <v>102.54</v>
       </c>
     </row>
-    <row r="723" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723">
         <v>523</v>
       </c>
@@ -37568,7 +37565,7 @@
         <v>126.48</v>
       </c>
     </row>
-    <row r="724" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724">
         <v>523</v>
       </c>
@@ -37615,7 +37612,7 @@
         <v>136.59</v>
       </c>
     </row>
-    <row r="725" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>524</v>
       </c>
@@ -37662,7 +37659,7 @@
         <v>99.38</v>
       </c>
     </row>
-    <row r="726" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726">
         <v>524</v>
       </c>
@@ -37709,7 +37706,7 @@
         <v>93.32</v>
       </c>
     </row>
-    <row r="727" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A727">
         <v>524</v>
       </c>
@@ -37756,7 +37753,7 @@
         <v>112.95</v>
       </c>
     </row>
-    <row r="728" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728">
         <v>524</v>
       </c>
@@ -37803,7 +37800,7 @@
         <v>178.12</v>
       </c>
     </row>
-    <row r="729" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729">
         <v>524</v>
       </c>
@@ -37850,7 +37847,7 @@
         <v>104.61</v>
       </c>
     </row>
-    <row r="730" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730">
         <v>524</v>
       </c>
@@ -37897,7 +37894,7 @@
         <v>74.31</v>
       </c>
     </row>
-    <row r="731" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731">
         <v>524</v>
       </c>
@@ -37944,7 +37941,7 @@
         <v>221.38</v>
       </c>
     </row>
-    <row r="732" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732" s="1">
         <v>526</v>
       </c>
@@ -37989,7 +37986,7 @@
         <v>96.6</v>
       </c>
     </row>
-    <row r="733" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733" s="1">
         <v>527</v>
       </c>
@@ -38034,7 +38031,7 @@
       </c>
       <c r="O733" s="3"/>
     </row>
-    <row r="734" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734" s="1">
         <v>528</v>
       </c>
@@ -38079,7 +38076,7 @@
       </c>
       <c r="O734" s="3"/>
     </row>
-    <row r="735" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>529</v>
       </c>
@@ -38126,7 +38123,7 @@
         <v>196.19</v>
       </c>
     </row>
-    <row r="736" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736">
         <v>529</v>
       </c>
@@ -38173,7 +38170,7 @@
         <v>96.19</v>
       </c>
     </row>
-    <row r="737" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737">
         <v>529</v>
       </c>
@@ -38220,7 +38217,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="738" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738" s="1">
         <v>530</v>
       </c>
@@ -38265,7 +38262,7 @@
       </c>
       <c r="O738" s="3"/>
     </row>
-    <row r="739" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739" s="1">
         <v>531</v>
       </c>
@@ -38310,7 +38307,7 @@
       </c>
       <c r="O739" s="3"/>
     </row>
-    <row r="740" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740" s="1">
         <v>532</v>
       </c>
@@ -38357,7 +38354,7 @@
         <v>133.15</v>
       </c>
     </row>
-    <row r="741" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741">
         <v>532</v>
       </c>
@@ -38404,7 +38401,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="742" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742">
         <v>532</v>
       </c>
@@ -38451,7 +38448,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="743" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743">
         <v>532</v>
       </c>
@@ -38498,7 +38495,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="744" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744">
         <v>532</v>
       </c>
@@ -38545,7 +38542,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="745" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>533</v>
       </c>
@@ -38592,7 +38589,7 @@
         <v>124.89</v>
       </c>
     </row>
-    <row r="746" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746">
         <v>533</v>
       </c>
@@ -38639,7 +38636,7 @@
         <v>103.75</v>
       </c>
     </row>
-    <row r="747" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A747">
         <v>533</v>
       </c>
@@ -38686,7 +38683,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="748" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A748" s="1">
         <v>534</v>
       </c>
@@ -38733,7 +38730,7 @@
         <v>134.09</v>
       </c>
     </row>
-    <row r="749" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A749">
         <v>534</v>
       </c>
@@ -38780,7 +38777,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="750" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750">
         <v>534</v>
       </c>
@@ -38827,7 +38824,7 @@
         <v>137.19999999999999</v>
       </c>
     </row>
-    <row r="751" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751" s="1">
         <v>535</v>
       </c>
@@ -38874,7 +38871,7 @@
         <v>132.66999999999999</v>
       </c>
     </row>
-    <row r="752" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752">
         <v>535</v>
       </c>
@@ -38921,7 +38918,7 @@
         <v>111.43</v>
       </c>
     </row>
-    <row r="753" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753">
         <v>535</v>
       </c>
@@ -38968,7 +38965,7 @@
         <v>151.25</v>
       </c>
     </row>
-    <row r="754" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754" s="1">
         <v>536</v>
       </c>
@@ -39015,7 +39012,7 @@
         <v>109.33</v>
       </c>
     </row>
-    <row r="755" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755">
         <v>536</v>
       </c>
@@ -39062,7 +39059,7 @@
         <v>111.43</v>
       </c>
     </row>
-    <row r="756" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756">
         <v>536</v>
       </c>
@@ -39109,7 +39106,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="757" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757" s="1">
         <v>537</v>
       </c>
@@ -39156,7 +39153,7 @@
         <v>58.9</v>
       </c>
     </row>
-    <row r="758" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758" s="1">
         <v>538</v>
       </c>
@@ -39201,7 +39198,7 @@
       </c>
       <c r="O758" s="3"/>
     </row>
-    <row r="759" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759" s="1">
         <v>539</v>
       </c>
@@ -39246,7 +39243,7 @@
       </c>
       <c r="O759" s="3"/>
     </row>
-    <row r="760" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760" s="1">
         <v>540</v>
       </c>
@@ -39293,7 +39290,7 @@
         <v>97.33</v>
       </c>
     </row>
-    <row r="761" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761" s="1">
         <v>541</v>
       </c>
@@ -39338,7 +39335,7 @@
       </c>
       <c r="O761" s="3"/>
     </row>
-    <row r="762" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>542</v>
       </c>
@@ -39385,7 +39382,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="763" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763">
         <v>542</v>
       </c>
@@ -39432,7 +39429,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="764" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764">
         <v>542</v>
       </c>
@@ -39479,7 +39476,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="765" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A765">
         <v>542</v>
       </c>
@@ -39526,7 +39523,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="766" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766">
         <v>542</v>
       </c>
@@ -39573,7 +39570,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="767" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767" s="1">
         <v>543</v>
       </c>
@@ -39618,7 +39615,7 @@
         <v>7.29</v>
       </c>
     </row>
-    <row r="768" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768">
         <v>543</v>
       </c>
@@ -39665,7 +39662,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="769" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769">
         <v>543</v>
       </c>
@@ -39712,7 +39709,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="770" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770" s="1">
         <v>544</v>
       </c>
@@ -39759,7 +39756,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="771" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771">
         <v>544</v>
       </c>
@@ -39806,7 +39803,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="772" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A772">
         <v>544</v>
       </c>
@@ -39853,7 +39850,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="773" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A773">
         <v>544</v>
       </c>
@@ -39900,7 +39897,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="774" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A774">
         <v>544</v>
       </c>
@@ -39947,7 +39944,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="775" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A775" s="1">
         <v>546</v>
       </c>
@@ -39992,7 +39989,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="776" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A776">
         <v>546</v>
       </c>
@@ -40036,7 +40033,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="777" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A777">
         <v>546</v>
       </c>
@@ -40080,7 +40077,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="778" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A778">
         <v>546</v>
       </c>
@@ -40124,7 +40121,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="779" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A779" s="1">
         <v>547</v>
       </c>
@@ -40169,7 +40166,7 @@
       </c>
       <c r="O779" s="3"/>
     </row>
-    <row r="780" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A780" s="1">
         <v>550</v>
       </c>
@@ -40216,7 +40213,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="781" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A781" s="1">
         <v>551</v>
       </c>
@@ -40263,7 +40260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="782" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>552</v>
       </c>
@@ -40308,7 +40305,7 @@
       </c>
       <c r="O782" s="3"/>
     </row>
-    <row r="783" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>553</v>
       </c>
@@ -40353,7 +40350,7 @@
       </c>
       <c r="O783" s="3"/>
     </row>
-    <row r="784" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>554</v>
       </c>
@@ -40398,7 +40395,7 @@
       </c>
       <c r="O784" s="3"/>
     </row>
-    <row r="785" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A785" s="1">
         <v>555</v>
       </c>
@@ -40443,7 +40440,7 @@
       </c>
       <c r="O785" s="3"/>
     </row>
-    <row r="786" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A786" s="1">
         <v>556</v>
       </c>
@@ -40490,6 +40487,13 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:O786" xr:uid="{15ED7BC6-9428-429B-AFE1-AE8C1E13D30C}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Comunicaciones Internas"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>

--- a/data/raw/Kawak/2026.xlsx
+++ b/data/raw/Kawak/2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67CCDDCC-836B-4FC4-8BAD-29B9ECFB6AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{611A9F7E-C278-462D-8C52-960A3E04ABAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5BF844A4-47DF-42C0-9733-69EE091E7B83}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97CA1CAF-51F3-44E5-B844-12C2CD0EA59D}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13293" uniqueCount="1353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13292" uniqueCount="1353">
   <si>
     <t>Id</t>
   </si>
@@ -4184,7 +4184,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{520AB3AC-52F3-4216-BBFD-CFDC58426EEB}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{845A459A-0CC8-4DA1-A3A6-0DA2D0480488}"/>
   </tableStyles>
   <colors>
     <indexedColors>
@@ -4581,7 +4581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A4BF59E-DF62-46C5-8305-3537D0B0CBA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A0DB6C-720D-4736-B5A9-896D584D78CC}">
   <dimension ref="A1:AA874"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>63</v>
@@ -17064,7 +17064,7 @@
       </c>
       <c r="J201" s="1"/>
       <c r="K201" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L201" s="1" t="s">
         <v>325</v>
@@ -22933,7 +22933,9 @@
       <c r="T297" s="7">
         <v>100</v>
       </c>
-      <c r="U297" s="3"/>
+      <c r="U297" s="7">
+        <v>99.64</v>
+      </c>
     </row>
     <row r="298" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
@@ -27345,7 +27347,9 @@
       <c r="T370" s="7">
         <v>106.13</v>
       </c>
-      <c r="U370" s="3"/>
+      <c r="U370" s="7">
+        <v>118.4</v>
+      </c>
     </row>
     <row r="371" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
@@ -33209,7 +33213,9 @@
         <v>320</v>
       </c>
       <c r="J465" s="1"/>
-      <c r="K465" s="1"/>
+      <c r="K465" s="1">
+        <v>90</v>
+      </c>
       <c r="L465" s="1" t="s">
         <v>778</v>
       </c>
@@ -33263,6 +33269,9 @@
       <c r="I466" t="s">
         <v>320</v>
       </c>
+      <c r="K466">
+        <v>90</v>
+      </c>
       <c r="L466" t="s">
         <v>778</v>
       </c>
@@ -33322,6 +33331,9 @@
       <c r="I467" t="s">
         <v>320</v>
       </c>
+      <c r="K467">
+        <v>90</v>
+      </c>
       <c r="L467" t="s">
         <v>778</v>
       </c>
@@ -33381,6 +33393,9 @@
       <c r="I468" t="s">
         <v>320</v>
       </c>
+      <c r="K468">
+        <v>90</v>
+      </c>
       <c r="L468" t="s">
         <v>778</v>
       </c>
@@ -33440,6 +33455,9 @@
       <c r="I469" t="s">
         <v>320</v>
       </c>
+      <c r="K469">
+        <v>90</v>
+      </c>
       <c r="L469" t="s">
         <v>778</v>
       </c>
@@ -33499,6 +33517,9 @@
       <c r="I470" t="s">
         <v>320</v>
       </c>
+      <c r="K470">
+        <v>90</v>
+      </c>
       <c r="L470" t="s">
         <v>778</v>
       </c>
@@ -33558,6 +33579,9 @@
       <c r="I471" t="s">
         <v>320</v>
       </c>
+      <c r="K471">
+        <v>90</v>
+      </c>
       <c r="L471" t="s">
         <v>778</v>
       </c>
@@ -33617,6 +33641,9 @@
       <c r="I472" t="s">
         <v>320</v>
       </c>
+      <c r="K472">
+        <v>90</v>
+      </c>
       <c r="L472" t="s">
         <v>778</v>
       </c>
@@ -33676,6 +33703,9 @@
       <c r="I473" t="s">
         <v>320</v>
       </c>
+      <c r="K473">
+        <v>90</v>
+      </c>
       <c r="L473" t="s">
         <v>778</v>
       </c>
@@ -33734,6 +33764,9 @@
       </c>
       <c r="I474" t="s">
         <v>320</v>
+      </c>
+      <c r="K474">
+        <v>90</v>
       </c>
       <c r="L474" t="s">
         <v>778</v>
@@ -35387,7 +35420,9 @@
       <c r="T500" s="7">
         <v>99</v>
       </c>
-      <c r="U500" s="3"/>
+      <c r="U500" s="7">
+        <v>99.5</v>
+      </c>
     </row>
     <row r="501" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A501" s="1">
@@ -42872,7 +42907,9 @@
         <v>826</v>
       </c>
       <c r="J625" s="1"/>
-      <c r="K625" s="1"/>
+      <c r="K625" s="1">
+        <v>90</v>
+      </c>
       <c r="L625" s="1" t="s">
         <v>920</v>
       </c>
@@ -45151,7 +45188,9 @@
       <c r="T664" s="7">
         <v>99</v>
       </c>
-      <c r="U664" s="3"/>
+      <c r="U664" s="9">
+        <v>98.95</v>
+      </c>
     </row>
     <row r="665" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
@@ -46850,7 +46889,7 @@
       </c>
       <c r="J693" s="1"/>
       <c r="K693" s="1">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="L693" s="1" t="s">
         <v>1028</v>
@@ -50013,7 +50052,7 @@
         <v>130</v>
       </c>
       <c r="F748" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G748" s="1" t="s">
         <v>26</v>
@@ -50074,7 +50113,7 @@
         <v>130</v>
       </c>
       <c r="F749" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G749" t="s">
         <v>26</v>
@@ -50136,7 +50175,7 @@
         <v>130</v>
       </c>
       <c r="F750" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G750" t="s">
         <v>26</v>
@@ -50198,7 +50237,7 @@
         <v>130</v>
       </c>
       <c r="F751" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G751" t="s">
         <v>26</v>
@@ -50260,7 +50299,7 @@
         <v>130</v>
       </c>
       <c r="F752" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G752" t="s">
         <v>26</v>
@@ -51090,7 +51129,9 @@
       <c r="R767" s="3"/>
       <c r="S767" s="3"/>
       <c r="T767" s="3"/>
-      <c r="U767" s="3"/>
+      <c r="U767" s="7">
+        <v>100</v>
+      </c>
     </row>
     <row r="768" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A768" s="1">
@@ -53958,9 +53999,7 @@
         <v>1113</v>
       </c>
       <c r="J818" s="1"/>
-      <c r="K818" s="1" t="s">
-        <v>132</v>
-      </c>
+      <c r="K818" s="1"/>
       <c r="L818" s="1" t="s">
         <v>1241</v>
       </c>
@@ -53978,7 +54017,9 @@
       <c r="R818" s="3"/>
       <c r="S818" s="3"/>
       <c r="T818" s="3"/>
-      <c r="U818" s="3"/>
+      <c r="U818" s="9">
+        <v>83.9</v>
+      </c>
     </row>
     <row r="819" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A819" s="1">
@@ -55924,7 +55965,9 @@
       <c r="R852" s="3"/>
       <c r="S852" s="3"/>
       <c r="T852" s="3"/>
-      <c r="U852" s="3"/>
+      <c r="U852" s="7">
+        <v>100</v>
+      </c>
     </row>
     <row r="853" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A853" s="1">

--- a/data/raw/Kawak/2026.xlsx
+++ b/data/raw/Kawak/2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BEB0794-0008-4A5E-829F-6A1AF21DA2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06226028-69D2-4D40-A276-70C6A39A58FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{615B2E1B-AEF4-455F-998B-FEF8A349233C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D216D6CF-1770-40B6-94ED-3F30F2F7053E}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11897" uniqueCount="1343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11921" uniqueCount="1348">
   <si>
     <t>Id</t>
   </si>
@@ -4060,6 +4060,21 @@
   </si>
   <si>
     <t>Consolidado Producción</t>
+  </si>
+  <si>
+    <t>Índice de Conformidad Normativa Contractual B2G</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>(NRAB2G/TRAB2G)*100</t>
+  </si>
+  <si>
+    <t>Índice de Conformidad Normativa Contractual Convenios</t>
+  </si>
+  <si>
+    <t>(NRCCV/TRACV)*100</t>
   </si>
 </sst>
 </file>
@@ -4154,7 +4169,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{B5BE7626-AA51-4C2B-86D4-7A3CAEC4862E}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{EBBC6B41-E8FE-4B29-B3E5-BAD37F030C0A}"/>
   </tableStyles>
   <colors>
     <indexedColors>
@@ -4551,8 +4566,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{845B83E9-764E-4A7D-B6ED-192FDC7FBB38}">
-  <dimension ref="A1:AA778"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0C5FA19-F0E3-45D4-9401-6F581CA9259C}">
+  <dimension ref="A1:AA780"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="27" width="9.109375" customWidth="1"/>
@@ -6820,7 +6835,9 @@
       <c r="U37" s="8">
         <v>191</v>
       </c>
-      <c r="V37" s="3"/>
+      <c r="V37" s="8">
+        <v>220</v>
+      </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
@@ -6884,7 +6901,9 @@
       <c r="U38" s="7">
         <v>1.95</v>
       </c>
-      <c r="V38" s="3"/>
+      <c r="V38" s="7">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
@@ -6948,7 +6967,9 @@
       <c r="U39" s="5">
         <v>1.62</v>
       </c>
-      <c r="V39" s="3"/>
+      <c r="V39" s="5">
+        <v>1.61</v>
+      </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
@@ -7012,7 +7033,9 @@
       <c r="U40" s="4">
         <v>133</v>
       </c>
-      <c r="V40" s="3"/>
+      <c r="V40" s="4">
+        <v>111.67</v>
+      </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
@@ -7108,7 +7131,7 @@
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>146</v>
@@ -7140,7 +7163,9 @@
       <c r="U42" s="4">
         <v>6.78</v>
       </c>
-      <c r="V42" s="3"/>
+      <c r="V42" s="4">
+        <v>8.17</v>
+      </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
@@ -40011,7 +40036,9 @@
       <c r="U552" s="4">
         <v>100</v>
       </c>
-      <c r="V552" s="3"/>
+      <c r="V552" s="4">
+        <v>100</v>
+      </c>
     </row>
     <row r="553" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
@@ -45093,7 +45120,9 @@
       <c r="U634" s="4">
         <v>95.5</v>
       </c>
-      <c r="V634" s="3"/>
+      <c r="V634" s="4">
+        <v>98.4</v>
+      </c>
     </row>
     <row r="635" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A635" s="1">
@@ -45149,7 +45178,9 @@
       <c r="U635" s="4">
         <v>100</v>
       </c>
-      <c r="V635" s="3"/>
+      <c r="V635" s="5">
+        <v>94.7</v>
+      </c>
     </row>
     <row r="636" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A636" s="1">
@@ -51200,7 +51231,7 @@
         <v>28</v>
       </c>
       <c r="I738" s="1" t="s">
-        <v>1082</v>
+        <v>1111</v>
       </c>
       <c r="J738" s="1"/>
       <c r="K738" s="1">
@@ -51252,7 +51283,7 @@
         <v>28</v>
       </c>
       <c r="I739" s="1" t="s">
-        <v>1082</v>
+        <v>1111</v>
       </c>
       <c r="J739" s="1"/>
       <c r="K739" s="1" t="s">
@@ -53547,6 +53578,110 @@
         <v>193</v>
       </c>
     </row>
+    <row r="779" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A779" s="1">
+        <v>630</v>
+      </c>
+      <c r="B779" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C779" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D779" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E779" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F779" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G779" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H779" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I779" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="J779" s="1"/>
+      <c r="K779" s="1">
+        <v>100</v>
+      </c>
+      <c r="L779" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="M779" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N779" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O779" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P779" s="3"/>
+      <c r="Q779" s="3"/>
+      <c r="R779" s="3"/>
+      <c r="S779" s="3"/>
+      <c r="T779" s="3"/>
+      <c r="U779" s="3"/>
+      <c r="V779" s="3"/>
+    </row>
+    <row r="780" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A780" s="1">
+        <v>631</v>
+      </c>
+      <c r="B780" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C780" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D780" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E780" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F780" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G780" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H780" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I780" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="J780" s="1"/>
+      <c r="K780" s="1">
+        <v>100</v>
+      </c>
+      <c r="L780" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="M780" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N780" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O780" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P780" s="3"/>
+      <c r="Q780" s="3"/>
+      <c r="R780" s="3"/>
+      <c r="S780" s="3"/>
+      <c r="T780" s="3"/>
+      <c r="U780" s="3"/>
+      <c r="V780" s="3"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
